--- a/testData/TC_Direct_CreateOpportunity_Step_Logger.xlsx
+++ b/testData/TC_Direct_CreateOpportunity_Step_Logger.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation_Project\E2E_Automation\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netapp-my.sharepoint.com/personal/sunilr2_netapp_com/Documents/Desktop/Playwright Python/E2E_Automation/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C704AE0F-0528-4FDE-A115-ED9DCE6DC8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{C704AE0F-0528-4FDE-A115-ED9DCE6DC8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D27A429A-DD92-471F-BFD1-4829EFFF7B12}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Primary Contact</t>
   </si>
@@ -54,9 +54,6 @@
     <t>End Customer Usage</t>
   </si>
   <si>
-    <t>Own Use</t>
-  </si>
-  <si>
     <t>Opportunity Type</t>
   </si>
   <si>
@@ -78,9 +75,6 @@
     <t>Standard</t>
   </si>
   <si>
-    <t>To be Determined Before Qualify Sales Stage</t>
-  </si>
-  <si>
     <t>Direct</t>
   </si>
   <si>
@@ -130,6 +124,9 @@
   </si>
   <si>
     <t>All SAN Array Flash Config</t>
+  </si>
+  <si>
+    <t>To be Determined at Qualify Sales Stage</t>
   </si>
 </sst>
 </file>
@@ -237,14 +234,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -555,7 +552,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -578,30 +575,30 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="S2" s="6"/>
+      <c r="S2" s="8"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
@@ -611,7 +608,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>1</v>
@@ -620,46 +617,46 @@
         <v>0</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>33</v>
+        <v>24</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.4">
@@ -670,7 +667,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>4</v>
@@ -679,33 +676,31 @@
         <v>5</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-      <c r="O4" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
-      <c r="R4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="S4" s="8">
+      <c r="R4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="6">
         <v>1000</v>
       </c>
     </row>
